--- a/output/2026-09-02_21_Italia_Molise_ATEX_Equipment-Services.xlsx
+++ b/output/2026-09-02_21_Italia_Molise_ATEX_Equipment-Services.xlsx
@@ -494,10 +494,9 @@
           <t>0874 62009</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Distributore forniture industriali generali (bulloneria, cuscinetti, utensileria, aria compressa/vuototecnica, pneumatica, saldatura) attivo dal 1990, P.IVA 00802630707. Esistenza confermata (registroaziende.it, paginegialle.it, ufficiocamerale.it). Nessuna evidenza diretta online di linea ATEX certificata: da verificare specificamente disponibilita' componentistica antideflagrante.</t>
+          <t>Distributore forniture industriali generali (bulloneria, cuscinetti, utensileria, aria compressa/vuototecnica, pneumatica, saldatura) attivo dal 1990, P.IVA 00802630707. Esistenza confermata (registroaziende.it, paginegialle.it, ufficiocamerale.it). Nessuna evidenza diretta online di linea ATEX certificata: da verificare specificamente disponibilita' componentistica antideflagrante. [DUPLICATO — vedi anche: 2026-09-02_16_Italia_Molise_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -532,10 +531,9 @@
           <t>0874 68311</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Distributore materiale elettrico/automazione industriale, parte del Gruppo Comet (rete nazionale 110+ punti vendita). Sede confermata Via Natale Molinari 6, CB. Nessuna conferma diretta online di linea ATEX/antideflagrante: da verificare.</t>
+          <t>Distributore materiale elettrico/automazione industriale, parte del Gruppo Comet (rete nazionale 110+ punti vendita). Sede confermata Via Natale Molinari 6, CB. Nessuna conferma diretta online di linea ATEX/antideflagrante: da verificare. [DUPLICATO — vedi anche: 2026-09-01_06_Italia_Umbria_ATEX_Equipment_Services.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -577,7 +575,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Distributore materiale elettrico civile/industriale dal 1981, parte del gruppo MEGA s.r.l. (rete Abruzzo-Molise). Esistenza confermata su piu' directory (telefono anche 0874 64044 riscontrato). Email non confermata/smentita da fonti indipendenti. Nessuna evidenza diretta di prodotti ATEX: da verificare.</t>
+          <t>Distributore materiale elettrico civile/industriale dal 1981, parte del gruppo MEGA s.r.l. (rete Abruzzo-Molise). Esistenza confermata su piu' directory (telefono anche 0874 64044 riscontrato). Email non confermata/smentita da fonti indipendenti. Nessuna evidenza diretta di prodotti ATEX: da verificare. [DUPLICATO — vedi anche: 2026-09-02_15_Italia_Molise_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -612,7 +610,6 @@
           <t>0874 699293</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>Ditta individuale (P.IVA 01514740701), impiantista elettrico civile/industriale con qualifiche per impianti elettrici e speciali. Esistenza confermata (amministrazionicomunali.it, paginebianche.it). Nessuna evidenza diretta di specializzazione in impianti in zone ATEX: da verificare.</t>
@@ -657,7 +654,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Attiva dal 1944, distributore forniture agricole/industriali (motori elettrici, elettropompe, compressori) di marchi terzi (Skf, Fag, Caprari, Comet), P.IVA 01652130707. ATTENZIONE: alcune directory la classificano anche come 'officina autoriparazioni'/'costruzioni meccaniche' - verificare umanamente se svolge anche attivita' propria di officina (cliente finale) oltre alla distribuzione. Email non confermata da fonti indipendenti. Nessuna evidenza diretta di prodotti ATEX.</t>
+          <t>Attiva dal 1944, distributore forniture agricole/industriali (motori elettrici, elettropompe, compressori) di marchi terzi (Skf, Fag, Caprari, Comet), P.IVA 01652130707. ATTENZIONE: alcune directory la classificano anche come 'officina autoriparazioni'/'costruzioni meccaniche' - verificare umanamente se svolge anche attivita' propria di officina (cliente finale) oltre alla distribuzione. Email non confermata da fonti indipendenti. Nessuna evidenza diretta di prodotti ATEX. [DUPLICATO — vedi anche: 2026-09-02_15_Italia_Molise_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -692,7 +689,6 @@
           <t>0865 909035 / 0865 902180</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>Azienda storica (dal 1965) del Gruppo Scarabeo, distributore materiale elettrico civile/industriale, energie alternative e fotovoltaico per il centro-sud Italia, certificata ISO 9001/ISO 14001. DEDUPLICATA con 'Elcom Elettrocommerciale S.p.A.' (Isernia, stesso gruppo/soci) - unificate in questa scheda. Nessuna evidenza diretta di linea prodotti ATEX certificata: da verificare.</t>
@@ -710,7 +706,6 @@
           <t>Calabrese Forniture Elettriche S.r.l.</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>Isernia</t>
@@ -726,7 +721,6 @@
           <t>0865 412415</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>Distributore/rivenditore materiale elettrico (illuminazione, materiale elettrico, apparecchiature energia elettrica), confermato su piu' directory (hotfrog.it, coobiz.it, paginebianche.it). Nessun sito web proprio rintracciato. Nessuna evidenza diretta di prodotti ATEX: da verificare.</t>
@@ -764,7 +758,6 @@
           <t>0865 904723</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>System integrator/installatore impianti elettrici industriali e civili, Venafro (IS). Esistenza confermata (Kompass, misterimprese.it). ATTENZIONE: esiste altra azienda omonima non correlata (siem.it, impianti aeroportuali/ospedalieri) - non confondere in fase di contatto. Nessuna evidenza diretta di specializzazione in impianti ATEX: da verificare.</t>
